--- a/src/data/RELAÇÃO DE CLIENTES - BITDEFENDER - FORTIGATE.xlsx
+++ b/src/data/RELAÇÃO DE CLIENTES - BITDEFENDER - FORTIGATE.xlsx
@@ -4205,8 +4205,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010073D834221BF66E498D0768B0CDCB4CA5" ma:contentTypeVersion="13" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="9a89451f6584c5fe678fae59eea7832a">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9dc4477a-76a2-4538-a1c8-03254231999a" xmlns:ns3="0c47f042-3dcc-45ca-9a7b-fcbd16c6ccea" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="9a00823e0ac3f54f5f036ea53c1c7418" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x01010073D834221BF66E498D0768B0CDCB4CA5" ma:contentTypeVersion="13" ma:contentTypeDescription="Crie um novo documento." ma:contentTypeScope="" ma:versionID="bbc4aa8a737aea1cedc95e203f4857a6">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9dc4477a-76a2-4538-a1c8-03254231999a" xmlns:ns3="0c47f042-3dcc-45ca-9a7b-fcbd16c6ccea" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1650bcde2918f5ed555fa669cae1c62e" ns2:_="" ns3:_="">
     <xsd:import namespace="9dc4477a-76a2-4538-a1c8-03254231999a"/>
     <xsd:import namespace="0c47f042-3dcc-45ca-9a7b-fcbd16c6ccea"/>
     <xsd:element name="properties">
@@ -4435,7 +4435,22 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1771E59-203E-4812-A5F1-6CB88B039623}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D5FFF654-9998-4FBD-B227-BEF16F245BC2}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="9dc4477a-76a2-4538-a1c8-03254231999a"/>
+    <ds:schemaRef ds:uri="0c47f042-3dcc-45ca-9a7b-fcbd16c6ccea"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
